--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Elezioni.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Elezioni.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <r>
       <t xml:space="preserve">
@@ -474,7 +474,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -536,8 +536,8 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. Puoi iscriverti nell'apposita lista elettorale dedicata se: 
-• hai diritto a votare nel tuo Stato di origine o di appartenenza; 
+      <t xml:space="preserve">. Puoi iscriverti nell'apposita lista elettorale dedicata se:
+• hai diritto a votare nel tuo Stato di origine o di appartenenza;
 • sei maggiorenne e residente nel Comune </t>
     </r>
     <r>
@@ -583,7 +583,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">  del </t>
+      <t xml:space="preserve"> del </t>
     </r>
     <r>
       <rPr>
@@ -600,7 +600,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">, puoi votare anche dall'estero. 
+      <t xml:space="preserve">, puoi votare anche dall'estero.
 Se sei all'estero da almeno tre mesi per motivi di lavoro, studio o cure mediche, puoi richiedere di votare per corrispondenza </t>
     </r>
     <r>
@@ -618,8 +618,8 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
-Se invece vivi all'estero da più di un anno e sei iscritto all'Anagrafe Italiani Residenti all'Estero (AIRE), scopri come puoi votare consultando il [sito](URL). 
+      <t xml:space="preserve">.
+Se invece vivi all'estero da più di un anno e sei iscritto all'Anagrafe Italiani Residenti all'Estero (AIRE), scopri come puoi votare consultando il [sito](URL).
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -698,8 +698,8 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
-Le richieste possono essere presentate anche da un delegato, scopri come [visitando questi sito](URL). 
+      <t xml:space="preserve">.
+Le richieste possono essere presentate anche da un delegato, scopri come [visitando questi sito](URL).
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -924,7 +924,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -989,9 +989,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
   </si>
 </sst>
 </file>
@@ -1777,7 +1774,7 @@
         <v>55</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
